--- a/artfynd/A 11357-2026 artfynd.xlsx
+++ b/artfynd/A 11357-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122746734</v>
+        <v>122746736</v>
       </c>
       <c r="B2" t="n">
-        <v>78735</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441126</v>
+        <v>441193</v>
       </c>
       <c r="R2" t="n">
-        <v>6849827</v>
+        <v>6849933</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122746732</v>
+        <v>122746734</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>78776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440999</v>
+        <v>441126</v>
       </c>
       <c r="R3" t="n">
-        <v>6849759</v>
+        <v>6849827</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122746733</v>
+        <v>122746732</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441072</v>
+        <v>440999</v>
       </c>
       <c r="R4" t="n">
-        <v>6849784</v>
+        <v>6849759</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,6 +971,208 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122746733</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långmyran V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>441072</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6849784</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sanna Strömberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122746731</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långmyran V, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>440944</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6849700</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sanna Strömberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
